--- a/src/data/calibration_data_green.xlsx
+++ b/src/data/calibration_data_green.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew Tan\Documents\ECSE211\ECSE211_W26_Final_Project\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1DC8E326-5457-4D40-8855-5B9078F465F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626F0CCB-526D-4A84-B0DB-3F2B6979ADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F3B7D0B3-C597-41A0-BB77-284A4C259954}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration_data_green" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>R</t>
   </si>
@@ -31,10 +44,16 @@
     <t>B</t>
   </si>
   <si>
-    <t>avg</t>
+    <t>vector avg</t>
   </si>
   <si>
-    <t>std dev</t>
+    <t>vector std dev</t>
+  </si>
+  <si>
+    <t>ratio avg</t>
+  </si>
+  <si>
+    <t>ratio std dev</t>
   </si>
 </sst>
 </file>
@@ -895,10 +914,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A1D262-0736-47BF-977A-4A1C3BC18EFF}">
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -909,7 +928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>37</v>
       </c>
@@ -931,23 +950,35 @@
         <f t="shared" si="0"/>
         <v>0.24552736699452146</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2">
+        <f>A2/($A2+$B2+$C2)</f>
+        <v>0.33636363636363636</v>
+      </c>
+      <c r="K2">
+        <f t="shared" ref="K2:L2" si="1">B2/($A2+$B2+$C2)</f>
+        <v>0.50909090909090904</v>
+      </c>
+      <c r="L2">
+        <f t="shared" si="1"/>
+        <v>0.15454545454545454</v>
+      </c>
+      <c r="N2" t="s">
         <v>3</v>
       </c>
-      <c r="K2">
+      <c r="O2">
         <f>AVERAGE(F2:F90)</f>
         <v>0.54072454058576835</v>
       </c>
-      <c r="L2">
-        <f t="shared" ref="L2:M2" si="1">AVERAGE(G2:G90)</f>
+      <c r="P2">
+        <f>AVERAGE(G2:G90)</f>
         <v>0.80082789721753345</v>
       </c>
-      <c r="M2">
-        <f t="shared" si="1"/>
+      <c r="Q2">
+        <f>AVERAGE(H2:H90)</f>
         <v>0.25696343843443153</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>38</v>
       </c>
@@ -969,23 +1000,35 @@
         <f t="shared" ref="H3:H66" si="4">C3/($A3^2 + $B3^2 + $C3^2)^0.5</f>
         <v>0.2672612419124244</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3">
+        <f t="shared" ref="J3:J66" si="5">A3/($A3+$B3+$C3)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="6">B3/($A3+$B3+$C3)</f>
+        <v>0.5</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L66" si="7">C3/($A3+$B3+$C3)</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N3" t="s">
         <v>4</v>
       </c>
-      <c r="K3">
+      <c r="O3">
         <f>_xlfn.STDEV.P(F2:F90)</f>
         <v>9.701897146230206E-3</v>
       </c>
-      <c r="L3">
-        <f t="shared" ref="L3:M3" si="5">_xlfn.STDEV.P(G2:G90)</f>
+      <c r="P3">
+        <f>_xlfn.STDEV.P(G2:G90)</f>
         <v>7.3591857745909902E-3</v>
       </c>
-      <c r="M3">
-        <f t="shared" si="5"/>
+      <c r="Q3">
+        <f>_xlfn.STDEV.P(H2:H90)</f>
         <v>1.0637534061367332E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>40</v>
       </c>
@@ -1007,8 +1050,20 @@
         <f t="shared" si="4"/>
         <v>0.24752939586124142</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <f t="shared" si="5"/>
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="7"/>
+        <v>0.15517241379310345</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>37</v>
       </c>
@@ -1030,8 +1085,35 @@
         <f t="shared" si="4"/>
         <v>0.2484201630456849</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <f t="shared" si="5"/>
+        <v>0.33944954128440369</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="6"/>
+        <v>0.50458715596330272</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="7"/>
+        <v>0.15596330275229359</v>
+      </c>
+      <c r="N5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <f>AVERAGE(J2:J90)</f>
+        <v>0.33826280130439562</v>
+      </c>
+      <c r="P5">
+        <f t="shared" ref="P5:Q5" si="8">AVERAGE(K2:K90)</f>
+        <v>0.50101268441909985</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="8"/>
+        <v>0.16072451427650419</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>38</v>
       </c>
@@ -1053,8 +1135,35 @@
         <f t="shared" si="4"/>
         <v>0.25126337053336062</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="6"/>
+        <v>0.50877192982456143</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="7"/>
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="N6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6">
+        <f>_xlfn.STDEV.P(J2:J90)</f>
+        <v>5.6076659960328842E-3</v>
+      </c>
+      <c r="P6">
+        <f t="shared" ref="P6:Q6" si="9">_xlfn.STDEV.P(K2:K90)</f>
+        <v>6.7615013536315967E-3</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="9"/>
+        <v>5.9524703024574745E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>37</v>
       </c>
@@ -1076,8 +1185,20 @@
         <f t="shared" si="4"/>
         <v>0.2484201630456849</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <f t="shared" si="5"/>
+        <v>0.33944954128440369</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="6"/>
+        <v>0.50458715596330272</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="7"/>
+        <v>0.15596330275229359</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>38</v>
       </c>
@@ -1099,8 +1220,20 @@
         <f t="shared" si="4"/>
         <v>0.25126337053336062</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="6"/>
+        <v>0.50877192982456143</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="7"/>
+        <v>0.15789473684210525</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>37</v>
       </c>
@@ -1122,8 +1255,20 @@
         <f t="shared" si="4"/>
         <v>0.2484201630456849</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <f t="shared" si="5"/>
+        <v>0.33944954128440369</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="6"/>
+        <v>0.50458715596330272</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="7"/>
+        <v>0.15596330275229359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>40</v>
       </c>
@@ -1145,8 +1290,20 @@
         <f t="shared" si="4"/>
         <v>0.27014696615770262</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <f t="shared" si="5"/>
+        <v>0.33613445378151263</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="6"/>
+        <v>0.49579831932773111</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="7"/>
+        <v>0.16806722689075632</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>36</v>
       </c>
@@ -1168,8 +1325,20 @@
         <f t="shared" si="4"/>
         <v>0.24741835845552387</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <f t="shared" si="5"/>
+        <v>0.33027522935779818</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="6"/>
+        <v>0.51376146788990829</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="7"/>
+        <v>0.15596330275229359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>40</v>
       </c>
@@ -1191,8 +1360,20 @@
         <f t="shared" si="4"/>
         <v>0.24752939586124142</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <f t="shared" si="5"/>
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="7"/>
+        <v>0.15517241379310345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>38</v>
       </c>
@@ -1214,8 +1395,20 @@
         <f t="shared" si="4"/>
         <v>0.25126337053336062</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="6"/>
+        <v>0.50877192982456143</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="7"/>
+        <v>0.15789473684210525</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>36</v>
       </c>
@@ -1237,8 +1430,20 @@
         <f t="shared" si="4"/>
         <v>0.21718612138153467</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="6"/>
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="7"/>
+        <v>0.1388888888888889</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>36</v>
       </c>
@@ -1260,8 +1465,20 @@
         <f t="shared" si="4"/>
         <v>0.24741835845552387</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <f t="shared" si="5"/>
+        <v>0.33027522935779818</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="6"/>
+        <v>0.51376146788990829</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="7"/>
+        <v>0.15596330275229359</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>39</v>
       </c>
@@ -1283,8 +1500,20 @@
         <f t="shared" si="4"/>
         <v>0.27211513994835923</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <f t="shared" si="5"/>
+        <v>0.33050847457627119</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="7"/>
+        <v>0.16949152542372881</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>36</v>
       </c>
@@ -1306,8 +1535,20 @@
         <f t="shared" si="4"/>
         <v>0.26100665575458371</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <f t="shared" si="5"/>
+        <v>0.32727272727272727</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="6"/>
+        <v>0.50909090909090904</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="7"/>
+        <v>0.16363636363636364</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>40</v>
       </c>
@@ -1329,8 +1570,20 @@
         <f t="shared" si="4"/>
         <v>0.27014696615770262</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <f t="shared" si="5"/>
+        <v>0.33613445378151263</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="6"/>
+        <v>0.49579831932773111</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="7"/>
+        <v>0.16806722689075632</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>38</v>
       </c>
@@ -1352,8 +1605,20 @@
         <f t="shared" si="4"/>
         <v>0.25126337053336062</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="6"/>
+        <v>0.50877192982456143</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="7"/>
+        <v>0.15789473684210525</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>39</v>
       </c>
@@ -1375,8 +1640,20 @@
         <f t="shared" si="4"/>
         <v>0.23901028055775114</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <f t="shared" si="5"/>
+        <v>0.34513274336283184</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="6"/>
+        <v>0.50442477876106195</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="7"/>
+        <v>0.15044247787610621</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>37</v>
       </c>
@@ -1398,8 +1675,20 @@
         <f t="shared" si="4"/>
         <v>0.2484201630456849</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <f t="shared" si="5"/>
+        <v>0.33944954128440369</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="6"/>
+        <v>0.50458715596330272</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="7"/>
+        <v>0.15596330275229359</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>37</v>
       </c>
@@ -1421,8 +1710,20 @@
         <f t="shared" si="4"/>
         <v>0.26926663176063015</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <f t="shared" si="5"/>
+        <v>0.32743362831858408</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="6"/>
+        <v>0.50442477876106195</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="7"/>
+        <v>0.16814159292035399</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>37</v>
       </c>
@@ -1444,8 +1745,20 @@
         <f t="shared" si="4"/>
         <v>0.25604785064734492</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <f t="shared" si="5"/>
+        <v>0.33035714285714285</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="6"/>
+        <v>0.5089285714285714</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="7"/>
+        <v>0.16071428571428573</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>39</v>
       </c>
@@ -1467,8 +1780,20 @@
         <f t="shared" si="4"/>
         <v>0.24939935524192006</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <f t="shared" si="5"/>
+        <v>0.33913043478260868</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="6"/>
+        <v>0.5043478260869565</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="7"/>
+        <v>0.15652173913043479</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>36</v>
       </c>
@@ -1490,8 +1815,20 @@
         <f t="shared" si="4"/>
         <v>0.24741835845552387</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <f t="shared" si="5"/>
+        <v>0.33027522935779818</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="6"/>
+        <v>0.51376146788990829</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="7"/>
+        <v>0.15596330275229359</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>38</v>
       </c>
@@ -1513,8 +1850,20 @@
         <f t="shared" si="4"/>
         <v>0.25126337053336062</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="6"/>
+        <v>0.50877192982456143</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="7"/>
+        <v>0.15789473684210525</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>38</v>
       </c>
@@ -1536,8 +1885,20 @@
         <f t="shared" si="4"/>
         <v>0.25412679227057289</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J27">
+        <f t="shared" si="5"/>
+        <v>0.33628318584070799</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="6"/>
+        <v>0.50442477876106195</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="7"/>
+        <v>0.15929203539823009</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>38</v>
       </c>
@@ -1559,8 +1920,20 @@
         <f t="shared" si="4"/>
         <v>0.2672612419124244</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>40</v>
       </c>
@@ -1582,8 +1955,20 @@
         <f t="shared" si="4"/>
         <v>0.24752939586124142</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <f t="shared" si="5"/>
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="7"/>
+        <v>0.15517241379310345</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>36</v>
       </c>
@@ -1605,8 +1990,20 @@
         <f t="shared" si="4"/>
         <v>0.26100665575458371</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <f t="shared" si="5"/>
+        <v>0.32727272727272727</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="6"/>
+        <v>0.50909090909090904</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="7"/>
+        <v>0.16363636363636364</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>38</v>
       </c>
@@ -1628,8 +2025,20 @@
         <f t="shared" si="4"/>
         <v>0.25412679227057289</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <f t="shared" si="5"/>
+        <v>0.33628318584070799</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="6"/>
+        <v>0.50442477876106195</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="7"/>
+        <v>0.15929203539823009</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>36</v>
       </c>
@@ -1651,8 +2060,20 @@
         <f t="shared" si="4"/>
         <v>0.23936651698576047</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <f t="shared" si="5"/>
+        <v>0.33962264150943394</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="6"/>
+        <v>0.50943396226415094</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="7"/>
+        <v>0.15094339622641509</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>38</v>
       </c>
@@ -1674,8 +2095,20 @@
         <f t="shared" si="4"/>
         <v>0.2599972716478845</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J33">
+        <f t="shared" si="5"/>
+        <v>0.34234234234234234</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="6"/>
+        <v>0.49549549549549549</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="7"/>
+        <v>0.16216216216216217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>36</v>
       </c>
@@ -1697,8 +2130,20 @@
         <f t="shared" si="4"/>
         <v>0.25339288424903944</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J34">
+        <f t="shared" si="5"/>
+        <v>0.3364485981308411</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="6"/>
+        <v>0.50467289719626163</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="7"/>
+        <v>0.15887850467289719</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>38</v>
       </c>
@@ -1720,8 +2165,20 @@
         <f t="shared" si="4"/>
         <v>0.25703796508989291</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J35">
+        <f t="shared" si="5"/>
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="7"/>
+        <v>0.16071428571428573</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>37</v>
       </c>
@@ -1743,8 +2200,20 @@
         <f t="shared" si="4"/>
         <v>0.27553599424027497</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J36">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="6"/>
+        <v>0.49549549549549549</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="7"/>
+        <v>0.17117117117117117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1766,8 +2235,20 @@
         <f t="shared" si="4"/>
         <v>0.25339288424903944</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <f t="shared" si="5"/>
+        <v>0.3364485981308411</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="6"/>
+        <v>0.50467289719626163</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="7"/>
+        <v>0.15887850467289719</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1789,8 +2270,20 @@
         <f t="shared" si="4"/>
         <v>0.2672612419124244</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J38">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1812,8 +2305,20 @@
         <f t="shared" si="4"/>
         <v>0.25703796508989291</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J39">
+        <f t="shared" si="5"/>
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="7"/>
+        <v>0.16071428571428573</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>37</v>
       </c>
@@ -1835,8 +2340,20 @@
         <f t="shared" si="4"/>
         <v>0.27553599424027497</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J40">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="6"/>
+        <v>0.49549549549549549</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="7"/>
+        <v>0.17117117117117117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>38</v>
       </c>
@@ -1858,8 +2375,20 @@
         <f t="shared" si="4"/>
         <v>0.25703796508989291</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J41">
+        <f t="shared" si="5"/>
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="7"/>
+        <v>0.16071428571428573</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>39</v>
       </c>
@@ -1881,8 +2410,20 @@
         <f t="shared" si="4"/>
         <v>0.26821821779200627</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J42">
+        <f t="shared" si="5"/>
+        <v>0.34210526315789475</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="6"/>
+        <v>0.49122807017543857</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>39</v>
       </c>
@@ -1904,8 +2445,20 @@
         <f t="shared" si="4"/>
         <v>0.25793366226088066</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J43">
+        <f t="shared" si="5"/>
+        <v>0.3482142857142857</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="6"/>
+        <v>0.49107142857142855</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="7"/>
+        <v>0.16071428571428573</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>38</v>
       </c>
@@ -1927,8 +2480,20 @@
         <f t="shared" si="4"/>
         <v>0.2599972716478845</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J44">
+        <f t="shared" si="5"/>
+        <v>0.34234234234234234</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="6"/>
+        <v>0.49549549549549549</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="7"/>
+        <v>0.16216216216216217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>39</v>
       </c>
@@ -1950,8 +2515,20 @@
         <f t="shared" si="4"/>
         <v>0.26821821779200627</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J45">
+        <f t="shared" si="5"/>
+        <v>0.34210526315789475</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="6"/>
+        <v>0.49122807017543857</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>35</v>
       </c>
@@ -1973,8 +2550,20 @@
         <f t="shared" si="4"/>
         <v>0.24732741107208978</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J46">
+        <f t="shared" si="5"/>
+        <v>0.33980582524271846</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="6"/>
+        <v>0.50485436893203883</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="7"/>
+        <v>0.1553398058252427</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>36</v>
       </c>
@@ -1996,8 +2585,20 @@
         <f t="shared" si="4"/>
         <v>0.25645956133454834</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J47">
+        <f t="shared" si="5"/>
+        <v>0.33962264150943394</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="7"/>
+        <v>0.16037735849056603</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>36</v>
       </c>
@@ -2019,8 +2620,20 @@
         <f t="shared" si="4"/>
         <v>0.25339288424903944</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J48">
+        <f t="shared" si="5"/>
+        <v>0.3364485981308411</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="6"/>
+        <v>0.50467289719626163</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="7"/>
+        <v>0.15887850467289719</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>37</v>
       </c>
@@ -2042,8 +2655,20 @@
         <f t="shared" si="4"/>
         <v>0.26513627537850831</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J49">
+        <f t="shared" si="5"/>
+        <v>0.33944954128440369</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="6"/>
+        <v>0.49541284403669728</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="7"/>
+        <v>0.16513761467889909</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>38</v>
       </c>
@@ -2065,8 +2690,20 @@
         <f t="shared" si="4"/>
         <v>0.2599972716478845</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J50">
+        <f t="shared" si="5"/>
+        <v>0.34234234234234234</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="6"/>
+        <v>0.49549549549549549</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="7"/>
+        <v>0.16216216216216217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>39</v>
       </c>
@@ -2088,8 +2725,20 @@
         <f t="shared" si="4"/>
         <v>0.26524829051793269</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J51">
+        <f t="shared" si="5"/>
+        <v>0.33913043478260868</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="6"/>
+        <v>0.4956521739130435</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="7"/>
+        <v>0.16521739130434782</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>37</v>
       </c>
@@ -2111,8 +2760,20 @@
         <f t="shared" si="4"/>
         <v>0.26513627537850831</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J52">
+        <f t="shared" si="5"/>
+        <v>0.33944954128440369</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="6"/>
+        <v>0.49541284403669728</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="7"/>
+        <v>0.16513761467889909</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>39</v>
       </c>
@@ -2134,8 +2795,20 @@
         <f t="shared" si="4"/>
         <v>0.26821821779200627</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J53">
+        <f t="shared" si="5"/>
+        <v>0.34210526315789475</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="6"/>
+        <v>0.49122807017543857</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>37</v>
       </c>
@@ -2157,8 +2830,20 @@
         <f t="shared" si="4"/>
         <v>0.25136270495976004</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J54">
+        <f t="shared" si="5"/>
+        <v>0.34259259259259262</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="7"/>
+        <v>0.15740740740740741</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>38</v>
       </c>
@@ -2180,8 +2865,20 @@
         <f t="shared" si="4"/>
         <v>0.27030007985833593</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J55">
+        <f t="shared" si="5"/>
+        <v>0.33628318584070799</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="6"/>
+        <v>0.49557522123893805</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="7"/>
+        <v>0.16814159292035399</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>38</v>
       </c>
@@ -2203,8 +2900,20 @@
         <f t="shared" si="4"/>
         <v>0.21639367524191511</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J56">
+        <f t="shared" si="5"/>
+        <v>0.34862385321100919</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="6"/>
+        <v>0.51376146788990829</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="7"/>
+        <v>0.13761467889908258</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>35</v>
       </c>
@@ -2226,8 +2935,20 @@
         <f t="shared" si="4"/>
         <v>0.25855700211031407</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J57">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="6"/>
+        <v>0.50476190476190474</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="7"/>
+        <v>0.16190476190476191</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>36</v>
       </c>
@@ -2249,8 +2970,20 @@
         <f t="shared" si="4"/>
         <v>0.25339288424903944</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J58">
+        <f t="shared" si="5"/>
+        <v>0.3364485981308411</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="6"/>
+        <v>0.50467289719626163</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="7"/>
+        <v>0.15887850467289719</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>35</v>
       </c>
@@ -2272,8 +3005,20 @@
         <f t="shared" si="4"/>
         <v>0.25541538778238687</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J59">
+        <f t="shared" si="5"/>
+        <v>0.330188679245283</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="6"/>
+        <v>0.50943396226415094</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="7"/>
+        <v>0.16037735849056603</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>38</v>
       </c>
@@ -2295,8 +3040,20 @@
         <f t="shared" si="4"/>
         <v>0.27030007985833593</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J60">
+        <f t="shared" si="5"/>
+        <v>0.33628318584070799</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="6"/>
+        <v>0.49557522123893805</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="7"/>
+        <v>0.16814159292035399</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>34</v>
       </c>
@@ -2318,8 +3075,20 @@
         <f t="shared" si="4"/>
         <v>0.24939187455541983</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J61">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="6"/>
+        <v>0.50980392156862742</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="7"/>
+        <v>0.15686274509803921</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>38</v>
       </c>
@@ -2341,8 +3110,20 @@
         <f t="shared" si="4"/>
         <v>0.27338836995775323</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J62">
+        <f t="shared" si="5"/>
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="6"/>
+        <v>0.49107142857142855</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="7"/>
+        <v>0.16964285714285715</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>35</v>
       </c>
@@ -2364,8 +3145,20 @@
         <f t="shared" si="4"/>
         <v>0.25855700211031407</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J63">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="6"/>
+        <v>0.50476190476190474</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="7"/>
+        <v>0.16190476190476191</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>38</v>
       </c>
@@ -2387,8 +3180,20 @@
         <f t="shared" si="4"/>
         <v>0.2599972716478845</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J64">
+        <f t="shared" si="5"/>
+        <v>0.34234234234234234</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="6"/>
+        <v>0.49549549549549549</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="7"/>
+        <v>0.16216216216216217</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>38</v>
       </c>
@@ -2410,8 +3215,20 @@
         <f t="shared" si="4"/>
         <v>0.27338836995775323</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J65">
+        <f t="shared" si="5"/>
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="6"/>
+        <v>0.49107142857142855</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="7"/>
+        <v>0.16964285714285715</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>38</v>
       </c>
@@ -2433,8 +3250,20 @@
         <f t="shared" si="4"/>
         <v>0.24932690632258411</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J66">
+        <f t="shared" si="5"/>
+        <v>0.34862385321100919</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="6"/>
+        <v>0.49541284403669728</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="7"/>
+        <v>0.15596330275229359</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>36</v>
       </c>
@@ -2445,19 +3274,31 @@
         <v>17</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F90" si="6">A67/($A67^2 + $B67^2 + $C67^2)^0.5</f>
+        <f t="shared" ref="F67:F90" si="10">A67/($A67^2 + $B67^2 + $C67^2)^0.5</f>
         <v>0.54969840604447262</v>
       </c>
       <c r="G67">
-        <f t="shared" ref="G67:G90" si="7">B67/($A67^2 + $B67^2 + $C67^2)^0.5</f>
+        <f t="shared" ref="G67:G90" si="11">B67/($A67^2 + $B67^2 + $C67^2)^0.5</f>
         <v>0.79400880873090496</v>
       </c>
       <c r="H67">
-        <f t="shared" ref="H67:H90" si="8">C67/($A67^2 + $B67^2 + $C67^2)^0.5</f>
+        <f t="shared" ref="H67:H90" si="12">C67/($A67^2 + $B67^2 + $C67^2)^0.5</f>
         <v>0.2595798028543343</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J67">
+        <f t="shared" ref="J67:J90" si="13">A67/($A67+$B67+$C67)</f>
+        <v>0.34285714285714286</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K90" si="14">B67/($A67+$B67+$C67)</f>
+        <v>0.49523809523809526</v>
+      </c>
+      <c r="L67">
+        <f t="shared" ref="L67:L90" si="15">C67/($A67+$B67+$C67)</f>
+        <v>0.16190476190476191</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>37</v>
       </c>
@@ -2468,19 +3309,31 @@
         <v>18</v>
       </c>
       <c r="F68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54500234383360047</v>
       </c>
       <c r="G68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79540882613552499</v>
       </c>
       <c r="H68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.26513627537850831</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J68">
+        <f t="shared" si="13"/>
+        <v>0.33944954128440369</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="14"/>
+        <v>0.49541284403669728</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="15"/>
+        <v>0.16513761467889909</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>38</v>
       </c>
@@ -2491,19 +3344,31 @@
         <v>19</v>
       </c>
       <c r="F69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54677673991550646</v>
       </c>
       <c r="G69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79138738671981201</v>
       </c>
       <c r="H69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.27338836995775323</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J69">
+        <f t="shared" si="13"/>
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="14"/>
+        <v>0.49107142857142855</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="15"/>
+        <v>0.16964285714285715</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>38</v>
       </c>
@@ -2514,19 +3379,31 @@
         <v>18</v>
       </c>
       <c r="F70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54888312903442282</v>
       </c>
       <c r="G70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79443610781298035</v>
       </c>
       <c r="H70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.2599972716478845</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J70">
+        <f t="shared" si="13"/>
+        <v>0.34234234234234234</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="14"/>
+        <v>0.49549549549549549</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="15"/>
+        <v>0.16216216216216217</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>38</v>
       </c>
@@ -2537,19 +3414,31 @@
         <v>18</v>
       </c>
       <c r="F71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54888312903442282</v>
       </c>
       <c r="G71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79443610781298035</v>
       </c>
       <c r="H71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.2599972716478845</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J71">
+        <f t="shared" si="13"/>
+        <v>0.34234234234234234</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="14"/>
+        <v>0.49549549549549549</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="15"/>
+        <v>0.16216216216216217</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>36</v>
       </c>
@@ -2560,19 +3449,31 @@
         <v>18</v>
       </c>
       <c r="F72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.52821367630570037</v>
       </c>
       <c r="G72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.80699311657815342</v>
       </c>
       <c r="H72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.26410683815285019</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J72">
+        <f t="shared" si="13"/>
+        <v>0.33027522935779818</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="14"/>
+        <v>0.50458715596330272</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="15"/>
+        <v>0.16513761467889909</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>37</v>
       </c>
@@ -2583,19 +3484,31 @@
         <v>18</v>
       </c>
       <c r="F73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53866995859241429</v>
       </c>
       <c r="G73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.80072561412385912</v>
       </c>
       <c r="H73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.26205565553144483</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J73">
+        <f t="shared" si="13"/>
+        <v>0.33636363636363636</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="15"/>
+        <v>0.16363636363636364</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>37</v>
       </c>
@@ -2606,19 +3519,31 @@
         <v>18</v>
       </c>
       <c r="F74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53866995859241429</v>
       </c>
       <c r="G74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.80072561412385912</v>
       </c>
       <c r="H74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.26205565553144483</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J74">
+        <f t="shared" si="13"/>
+        <v>0.33636363636363636</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L74">
+        <f t="shared" si="15"/>
+        <v>0.16363636363636364</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>38</v>
       </c>
@@ -2629,19 +3554,31 @@
         <v>18</v>
       </c>
       <c r="F75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54263570407866279</v>
       </c>
       <c r="G75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79967366916855576</v>
       </c>
       <c r="H75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.25703796508989291</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J75">
+        <f t="shared" si="13"/>
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L75">
+        <f t="shared" si="15"/>
+        <v>0.16071428571428573</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>36</v>
       </c>
@@ -2652,19 +3589,31 @@
         <v>18</v>
       </c>
       <c r="F76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53452248382484879</v>
       </c>
       <c r="G76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.80178372573727319</v>
       </c>
       <c r="H76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.2672612419124244</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J76">
+        <f t="shared" si="13"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L76">
+        <f t="shared" si="15"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>36</v>
       </c>
@@ -2675,19 +3624,31 @@
         <v>17</v>
       </c>
       <c r="F77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.5430908357672789</v>
       </c>
       <c r="G77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79955039710182729</v>
       </c>
       <c r="H77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.25645956133454834</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J77">
+        <f t="shared" si="13"/>
+        <v>0.33962264150943394</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="15"/>
+        <v>0.16037735849056603</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>38</v>
       </c>
@@ -2698,19 +3659,31 @@
         <v>17</v>
       </c>
       <c r="F78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.55731896707401152</v>
       </c>
       <c r="G78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79197958478938479</v>
       </c>
       <c r="H78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.24932690632258411</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J78">
+        <f t="shared" si="13"/>
+        <v>0.34862385321100919</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="14"/>
+        <v>0.49541284403669728</v>
+      </c>
+      <c r="L78">
+        <f t="shared" si="15"/>
+        <v>0.15596330275229359</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>35</v>
       </c>
@@ -2721,19 +3694,31 @@
         <v>18</v>
       </c>
       <c r="F79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53018133138454815</v>
       </c>
       <c r="G79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.80284601609660144</v>
       </c>
       <c r="H79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.2726646847120533</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J79">
+        <f t="shared" si="13"/>
+        <v>0.330188679245283</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L79">
+        <f t="shared" si="15"/>
+        <v>0.16981132075471697</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>35</v>
       </c>
@@ -2744,19 +3729,31 @@
         <v>16</v>
       </c>
       <c r="F80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.5478120035019256</v>
       </c>
       <c r="G80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79824034795994869</v>
       </c>
       <c r="H80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.25042834445802314</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J80">
+        <f t="shared" si="13"/>
+        <v>0.34313725490196079</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L80">
+        <f t="shared" si="15"/>
+        <v>0.15686274509803921</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>37</v>
       </c>
@@ -2767,19 +3764,31 @@
         <v>17</v>
       </c>
       <c r="F81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54708353432418355</v>
       </c>
       <c r="G81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79844623928394354</v>
       </c>
       <c r="H81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.25136270495976004</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J81">
+        <f t="shared" si="13"/>
+        <v>0.34259259259259262</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="15"/>
+        <v>0.15740740740740741</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>37</v>
       </c>
@@ -2790,19 +3799,31 @@
         <v>18</v>
       </c>
       <c r="F82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54500234383360047</v>
       </c>
       <c r="G82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79540882613552499</v>
       </c>
       <c r="H82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.26513627537850831</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J82">
+        <f t="shared" si="13"/>
+        <v>0.33944954128440369</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="14"/>
+        <v>0.49541284403669728</v>
+      </c>
+      <c r="L82">
+        <f t="shared" si="15"/>
+        <v>0.16513761467889909</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>38</v>
       </c>
@@ -2813,19 +3834,31 @@
         <v>17</v>
       </c>
       <c r="F83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.56384538699144116</v>
       </c>
       <c r="G83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.78641593448806257</v>
       </c>
       <c r="H83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.25224662049617103</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J83">
+        <f t="shared" si="13"/>
+        <v>0.35185185185185186</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="14"/>
+        <v>0.49074074074074076</v>
+      </c>
+      <c r="L83">
+        <f t="shared" si="15"/>
+        <v>0.15740740740740741</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>39</v>
       </c>
@@ -2836,19 +3869,31 @@
         <v>18</v>
       </c>
       <c r="F84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.56521739130434778</v>
       </c>
       <c r="G84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.78260869565217395</v>
       </c>
       <c r="H84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.2608695652173913</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J84">
+        <f t="shared" si="13"/>
+        <v>0.35135135135135137</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="14"/>
+        <v>0.48648648648648651</v>
+      </c>
+      <c r="L84">
+        <f t="shared" si="15"/>
+        <v>0.16216216216216217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>38</v>
       </c>
@@ -2859,19 +3904,31 @@
         <v>17</v>
       </c>
       <c r="F85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.55731896707401152</v>
       </c>
       <c r="G85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79197958478938479</v>
       </c>
       <c r="H85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.24932690632258411</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J85">
+        <f t="shared" si="13"/>
+        <v>0.34862385321100919</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="14"/>
+        <v>0.49541284403669728</v>
+      </c>
+      <c r="L85">
+        <f t="shared" si="15"/>
+        <v>0.15596330275229359</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>37</v>
       </c>
@@ -2882,19 +3939,31 @@
         <v>18</v>
       </c>
       <c r="F86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53866995859241429</v>
       </c>
       <c r="G86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.80072561412385912</v>
       </c>
       <c r="H86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.26205565553144483</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J86">
+        <f t="shared" si="13"/>
+        <v>0.33636363636363636</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L86">
+        <f t="shared" si="15"/>
+        <v>0.16363636363636364</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>37</v>
       </c>
@@ -2905,19 +3974,31 @@
         <v>17</v>
       </c>
       <c r="F87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.55359702531968391</v>
       </c>
       <c r="G87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79299033356603377</v>
       </c>
       <c r="H87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.25435539001174667</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J87">
+        <f t="shared" si="13"/>
+        <v>0.34579439252336447</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="14"/>
+        <v>0.49532710280373832</v>
+      </c>
+      <c r="L87">
+        <f t="shared" si="15"/>
+        <v>0.15887850467289719</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>37</v>
       </c>
@@ -2928,19 +4009,31 @@
         <v>16</v>
       </c>
       <c r="F88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.55565327662580077</v>
       </c>
       <c r="G88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79593577462614706</v>
       </c>
       <c r="H88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.24028249800034629</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J88">
+        <f t="shared" si="13"/>
+        <v>0.34905660377358488</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L88">
+        <f t="shared" si="15"/>
+        <v>0.15094339622641509</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>36</v>
       </c>
@@ -2951,19 +4044,31 @@
         <v>17</v>
       </c>
       <c r="F89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.5430908357672789</v>
       </c>
       <c r="G89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.79955039710182729</v>
       </c>
       <c r="H89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.25645956133454834</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J89">
+        <f t="shared" si="13"/>
+        <v>0.33962264150943394</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="L89">
+        <f t="shared" si="15"/>
+        <v>0.16037735849056603</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>37</v>
       </c>
@@ -2974,16 +4079,28 @@
         <v>18</v>
       </c>
       <c r="F90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53244299951492435</v>
       </c>
       <c r="G90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.80585967494150712</v>
       </c>
       <c r="H90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.25902632408834159</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="13"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="14"/>
+        <v>0.50450450450450446</v>
+      </c>
+      <c r="L90">
+        <f t="shared" si="15"/>
+        <v>0.16216216216216217</v>
       </c>
     </row>
   </sheetData>
